--- a/output/tables/universal_sm_hybrid/hybrid_distributional_incidence.xlsx
+++ b/output/tables/universal_sm_hybrid/hybrid_distributional_incidence.xlsx
@@ -466,43 +466,43 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>448</v>
+        <v>402</v>
       </c>
       <c r="C2" t="n">
-        <v>4.43433371412791</v>
+        <v>4.97046232466456</v>
       </c>
       <c r="D2" t="n">
-        <v>-141188.275</v>
+        <v>-49518</v>
       </c>
       <c r="E2" t="n">
-        <v>7301.24</v>
+        <v>7704</v>
       </c>
       <c r="F2" t="n">
-        <v>12553.105</v>
+        <v>12801</v>
       </c>
       <c r="G2" t="n">
-        <v>172.060708135807</v>
+        <v>171.501873084346</v>
       </c>
       <c r="H2" t="n">
-        <v>518.233667043824</v>
+        <v>527.086997240057</v>
       </c>
       <c r="I2" t="n">
-        <v>2298.02102156857</v>
+        <v>2619.86606160227</v>
       </c>
       <c r="J2" t="n">
-        <v>443.433371412791</v>
+        <v>497.046232466456</v>
       </c>
       <c r="K2" t="n">
-        <v>2741.45439298136</v>
+        <v>3116.91229406873</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0962900211632315</v>
+        <v>0.0993636200114733</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0997096287799104</v>
+        <v>0.0998436569166207</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0968271564732164</v>
+        <v>0.0994398607087255</v>
       </c>
     </row>
     <row r="3">
@@ -510,43 +510,43 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>439</v>
+        <v>394</v>
       </c>
       <c r="C3" t="n">
-        <v>4.45622329904797</v>
+        <v>4.98350628225641</v>
       </c>
       <c r="D3" t="n">
-        <v>12568.407</v>
+        <v>12857</v>
       </c>
       <c r="E3" t="n">
-        <v>16434.348</v>
+        <v>17184</v>
       </c>
       <c r="F3" t="n">
-        <v>19962.552</v>
+        <v>20713</v>
       </c>
       <c r="G3" t="n">
-        <v>129.324441794024</v>
+        <v>125.612441820865</v>
       </c>
       <c r="H3" t="n">
-        <v>653.195073778606</v>
+        <v>655.621497414658</v>
       </c>
       <c r="I3" t="n">
-        <v>2910.78310659558</v>
+        <v>3267.2938511483</v>
       </c>
       <c r="J3" t="n">
-        <v>445.622329904797</v>
+        <v>498.350628225641</v>
       </c>
       <c r="K3" t="n">
-        <v>3356.40543650038</v>
+        <v>3765.64447937394</v>
       </c>
       <c r="L3" t="n">
-        <v>0.121965536566047</v>
+        <v>0.123918603874265</v>
       </c>
       <c r="M3" t="n">
-        <v>0.100201834041678</v>
+        <v>0.100105676089399</v>
       </c>
       <c r="N3" t="n">
-        <v>0.118547000168821</v>
+        <v>0.120136573371053</v>
       </c>
     </row>
     <row r="4">
@@ -554,43 +554,43 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C4" t="n">
-        <v>4.44154325612709</v>
+        <v>4.97603879679499</v>
       </c>
       <c r="D4" t="n">
-        <v>19964.738</v>
+        <v>20713</v>
       </c>
       <c r="E4" t="n">
-        <v>22795.608</v>
+        <v>23605</v>
       </c>
       <c r="F4" t="n">
-        <v>25536.852</v>
+        <v>26664</v>
       </c>
       <c r="G4" t="n">
-        <v>98.1724704345243</v>
+        <v>97.7772732432739</v>
       </c>
       <c r="H4" t="n">
-        <v>675.386583059987</v>
+        <v>701.624643376364</v>
       </c>
       <c r="I4" t="n">
-        <v>2999.7587232688</v>
+        <v>3491.31144622823</v>
       </c>
       <c r="J4" t="n">
-        <v>444.154325612709</v>
+        <v>497.603879679499</v>
       </c>
       <c r="K4" t="n">
-        <v>3443.91304888151</v>
+        <v>3988.91532590773</v>
       </c>
       <c r="L4" t="n">
-        <v>0.125693728750568</v>
+        <v>0.132414915773429</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0998717412420648</v>
+        <v>0.0999556737339362</v>
       </c>
       <c r="N4" t="n">
-        <v>0.121637736713014</v>
+        <v>0.127259655378169</v>
       </c>
     </row>
     <row r="5">
@@ -598,43 +598,43 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>458</v>
+        <v>418</v>
       </c>
       <c r="C5" t="n">
-        <v>4.45229041082673</v>
+        <v>4.97490197347947</v>
       </c>
       <c r="D5" t="n">
-        <v>25539.038</v>
+        <v>26664</v>
       </c>
       <c r="E5" t="n">
-        <v>27974.242</v>
+        <v>29280</v>
       </c>
       <c r="F5" t="n">
-        <v>30655.371</v>
+        <v>31561</v>
       </c>
       <c r="G5" t="n">
-        <v>73.4797649732394</v>
+        <v>71.4042456578499</v>
       </c>
       <c r="H5" t="n">
-        <v>667.016637222493</v>
+        <v>638.832206033196</v>
       </c>
       <c r="I5" t="n">
-        <v>2969.7517777676</v>
+        <v>3178.12760251679</v>
       </c>
       <c r="J5" t="n">
-        <v>445.229041082673</v>
+        <v>497.490197347947</v>
       </c>
       <c r="K5" t="n">
-        <v>3414.98081885027</v>
+        <v>3675.61779986474</v>
       </c>
       <c r="L5" t="n">
-        <v>0.124436399339637</v>
+        <v>0.120536796927443</v>
       </c>
       <c r="M5" t="n">
-        <v>0.100113399825885</v>
+        <v>0.099932837911094</v>
       </c>
       <c r="N5" t="n">
-        <v>0.120615861035809</v>
+        <v>0.117264423106351</v>
       </c>
     </row>
     <row r="6">
@@ -642,43 +642,43 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="C6" t="n">
-        <v>4.45096689800677</v>
+        <v>4.97990937244596</v>
       </c>
       <c r="D6" t="n">
-        <v>30689.254</v>
+        <v>31572</v>
       </c>
       <c r="E6" t="n">
-        <v>32999.856</v>
+        <v>34148</v>
       </c>
       <c r="F6" t="n">
-        <v>34783.632</v>
+        <v>36296</v>
       </c>
       <c r="G6" t="n">
-        <v>48.8226617649368</v>
+        <v>47.9645816778295</v>
       </c>
       <c r="H6" t="n">
-        <v>558.27367972807</v>
+        <v>537.176617753478</v>
       </c>
       <c r="I6" t="n">
-        <v>2484.85766849807</v>
+        <v>2675.09087340937</v>
       </c>
       <c r="J6" t="n">
-        <v>445.096689800677</v>
+        <v>497.990937244596</v>
       </c>
       <c r="K6" t="n">
-        <v>2929.95435829875</v>
+        <v>3173.08181065396</v>
       </c>
       <c r="L6" t="n">
-        <v>0.104118715730451</v>
+        <v>0.101458130603457</v>
       </c>
       <c r="M6" t="n">
-        <v>0.100083639555127</v>
+        <v>0.10003342352905</v>
       </c>
       <c r="N6" t="n">
-        <v>0.103484905616777</v>
+        <v>0.10123185495763</v>
       </c>
     </row>
     <row r="7">
@@ -686,43 +686,43 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="C7" t="n">
-        <v>4.44582902388394</v>
+        <v>4.97743940641116</v>
       </c>
       <c r="D7" t="n">
-        <v>34784.725</v>
+        <v>36316</v>
       </c>
       <c r="E7" t="n">
-        <v>37039.584</v>
+        <v>38509</v>
       </c>
       <c r="F7" t="n">
-        <v>38940.311</v>
+        <v>40680</v>
       </c>
       <c r="G7" t="n">
-        <v>30.268801925026</v>
+        <v>29.0657282324895</v>
       </c>
       <c r="H7" t="n">
-        <v>434.886008821099</v>
+        <v>452.305354342448</v>
       </c>
       <c r="I7" t="n">
-        <v>1933.42884009789</v>
+        <v>2251.32249443486</v>
       </c>
       <c r="J7" t="n">
-        <v>444.582902388394</v>
+        <v>497.743940641116</v>
       </c>
       <c r="K7" t="n">
-        <v>2378.01174248628</v>
+        <v>2749.06643507598</v>
       </c>
       <c r="L7" t="n">
-        <v>0.081013142257312</v>
+        <v>0.0853858737814621</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0999681102435026</v>
+        <v>0.0999838083372903</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0839904963126013</v>
+        <v>0.087704355333702</v>
       </c>
     </row>
     <row r="8">
@@ -730,43 +730,43 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>466</v>
+        <v>421</v>
       </c>
       <c r="C8" t="n">
-        <v>4.44939062397037</v>
+        <v>4.9839348180539</v>
       </c>
       <c r="D8" t="n">
-        <v>38965.45</v>
+        <v>40686</v>
       </c>
       <c r="E8" t="n">
-        <v>41039.964</v>
+        <v>42377</v>
       </c>
       <c r="F8" t="n">
-        <v>43886.136</v>
+        <v>45276</v>
       </c>
       <c r="G8" t="n">
-        <v>14.8072520584336</v>
+        <v>10.6391190827563</v>
       </c>
       <c r="H8" t="n">
-        <v>354.772265564442</v>
+        <v>342.421066066296</v>
       </c>
       <c r="I8" t="n">
-        <v>1578.52039204715</v>
+        <v>1706.60427360295</v>
       </c>
       <c r="J8" t="n">
-        <v>444.939062397037</v>
+        <v>498.39348180539</v>
       </c>
       <c r="K8" t="n">
-        <v>2023.45945444419</v>
+        <v>2204.99775540833</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0661420241722004</v>
+        <v>0.0647263541589336</v>
       </c>
       <c r="M8" t="n">
-        <v>0.100048195741206</v>
+        <v>0.100114284258689</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0714678404697462</v>
+        <v>0.070346756332574</v>
       </c>
     </row>
     <row r="9">
@@ -774,43 +774,43 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>448</v>
+        <v>477</v>
       </c>
       <c r="C9" t="n">
-        <v>4.4436894162443</v>
+        <v>4.97466669620867</v>
       </c>
       <c r="D9" t="n">
-        <v>43912.368</v>
+        <v>45276</v>
       </c>
       <c r="E9" t="n">
-        <v>50666.015</v>
+        <v>51988</v>
       </c>
       <c r="F9" t="n">
-        <v>55842.463</v>
+        <v>59077</v>
       </c>
       <c r="G9" t="n">
-        <v>73.02202172061</v>
+        <v>71.8991940061301</v>
       </c>
       <c r="H9" t="n">
-        <v>693.41626230478</v>
+        <v>697.949253196684</v>
       </c>
       <c r="I9" t="n">
-        <v>3081.32650585543</v>
+        <v>3472.06490552126</v>
       </c>
       <c r="J9" t="n">
-        <v>444.36894162443</v>
+        <v>497.466669620867</v>
       </c>
       <c r="K9" t="n">
-        <v>3525.69544747986</v>
+        <v>3969.53157514212</v>
       </c>
       <c r="L9" t="n">
-        <v>0.129111523208402</v>
+        <v>0.131684952518676</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0999199994116985</v>
+        <v>0.0999281118028225</v>
       </c>
       <c r="N9" t="n">
-        <v>0.12452626082128</v>
+        <v>0.126641249310147</v>
       </c>
     </row>
     <row r="10">
@@ -818,43 +818,43 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>496</v>
+        <v>461</v>
       </c>
       <c r="C10" t="n">
-        <v>4.44806443106848</v>
+        <v>4.97580737290456</v>
       </c>
       <c r="D10" t="n">
-        <v>55847.928</v>
+        <v>59100</v>
       </c>
       <c r="E10" t="n">
-        <v>61893.311</v>
+        <v>65244</v>
       </c>
       <c r="F10" t="n">
-        <v>69351.943</v>
+        <v>73104</v>
       </c>
       <c r="G10" t="n">
-        <v>49.5550509691438</v>
+        <v>46.3253490748098</v>
       </c>
       <c r="H10" t="n">
-        <v>553.028149161065</v>
+        <v>509.925534760181</v>
       </c>
       <c r="I10" t="n">
-        <v>2459.90483966297</v>
+        <v>2537.29123549201</v>
       </c>
       <c r="J10" t="n">
-        <v>444.806443106848</v>
+        <v>497.580737290456</v>
       </c>
       <c r="K10" t="n">
-        <v>2904.71128276982</v>
+        <v>3034.87197278246</v>
       </c>
       <c r="L10" t="n">
-        <v>0.103073160274663</v>
+        <v>0.0962318058457079</v>
       </c>
       <c r="M10" t="n">
-        <v>0.100018375206609</v>
+        <v>0.0999510250300512</v>
       </c>
       <c r="N10" t="n">
-        <v>0.102593329513829</v>
+        <v>0.0968225018126379</v>
       </c>
     </row>
     <row r="11">
@@ -862,43 +862,43 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>528</v>
+        <v>417</v>
       </c>
       <c r="C11" t="n">
-        <v>4.45014132869324</v>
+        <v>4.9857876280409</v>
       </c>
       <c r="D11" t="n">
-        <v>69357.408</v>
+        <v>73128</v>
       </c>
       <c r="E11" t="n">
-        <v>77789.903</v>
+        <v>80364</v>
       </c>
       <c r="F11" t="n">
-        <v>85948.055</v>
+        <v>88084</v>
       </c>
       <c r="G11" t="n">
-        <v>19.0108609284134</v>
+        <v>17.5411510954705</v>
       </c>
       <c r="H11" t="n">
-        <v>258.253995518046</v>
+        <v>234.161336140363</v>
       </c>
       <c r="I11" t="n">
-        <v>1149.26677875501</v>
+        <v>1167.47869269415</v>
       </c>
       <c r="J11" t="n">
-        <v>445.014132869324</v>
+        <v>498.57876280409</v>
       </c>
       <c r="K11" t="n">
-        <v>1594.28091162434</v>
+        <v>1666.05745549824</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0481557485374889</v>
+        <v>0.044278946505153</v>
       </c>
       <c r="M11" t="n">
-        <v>0.100065075952319</v>
+        <v>0.100151502391046</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0563094128749059</v>
+        <v>0.0531527696890098</v>
       </c>
     </row>
   </sheetData>
@@ -964,46 +964,46 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1430</v>
+        <v>1165</v>
       </c>
       <c r="C2" t="n">
-        <v>14.5282545657152</v>
+        <v>14.4173636593078</v>
       </c>
       <c r="D2" t="n">
-        <v>14.5282545657152</v>
+        <v>14.4173636593078</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>-141188.275</v>
+        <v>-49518</v>
       </c>
       <c r="G2" t="n">
-        <v>17221.308</v>
+        <v>16732</v>
       </c>
       <c r="H2" t="n">
-        <v>26861.568</v>
+        <v>26148</v>
       </c>
       <c r="I2" t="n">
-        <v>623.655609783921</v>
+        <v>625.337233461198</v>
       </c>
       <c r="J2" t="n">
-        <v>9060.62746027714</v>
+        <v>9015.71430451555</v>
       </c>
       <c r="K2" t="n">
-        <v>1452.82545657152</v>
+        <v>1441.73636593078</v>
       </c>
       <c r="L2" t="n">
-        <v>10513.4529168487</v>
+        <v>10457.4506704463</v>
       </c>
       <c r="M2" t="n">
-        <v>0.379651883822513</v>
+        <v>0.341938858407902</v>
       </c>
       <c r="N2" t="n">
-        <v>0.326679714012547</v>
+        <v>0.28960732761197</v>
       </c>
       <c r="O2" t="n">
-        <v>0.371331273378007</v>
+        <v>0.3336274299461</v>
       </c>
     </row>
     <row r="3">
@@ -1011,46 +1011,46 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>1439</v>
+        <v>1256</v>
       </c>
       <c r="C3" t="n">
-        <v>14.5345270602777</v>
+        <v>14.4226728700571</v>
       </c>
       <c r="D3" t="n">
-        <v>14.5345270602777</v>
+        <v>14.4226728700571</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>26909.66</v>
+        <v>26148</v>
       </c>
       <c r="G3" t="n">
-        <v>34272.108</v>
+        <v>33468</v>
       </c>
       <c r="H3" t="n">
-        <v>41081.498</v>
+        <v>39864</v>
       </c>
       <c r="I3" t="n">
-        <v>501.997435171046</v>
+        <v>559.364442479493</v>
       </c>
       <c r="J3" t="n">
-        <v>7296.29530568355</v>
+        <v>8067.53036902362</v>
       </c>
       <c r="K3" t="n">
-        <v>1453.45270602777</v>
+        <v>1442.26728700571</v>
       </c>
       <c r="L3" t="n">
-        <v>8749.74801171132</v>
+        <v>9509.79765602933</v>
       </c>
       <c r="M3" t="n">
-        <v>0.305724109050102</v>
+        <v>0.305977100802025</v>
       </c>
       <c r="N3" t="n">
-        <v>0.326820756194906</v>
+        <v>0.289713975843448</v>
       </c>
       <c r="O3" t="n">
-        <v>0.309037867637052</v>
+        <v>0.303394149422566</v>
       </c>
     </row>
     <row r="4">
@@ -1058,46 +1058,46 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>1490</v>
+        <v>1270</v>
       </c>
       <c r="C4" t="n">
-        <v>14.5338139186254</v>
+        <v>14.4140284997496</v>
       </c>
       <c r="D4" t="n">
-        <v>6.06203075849541</v>
+        <v>8.59471699589223</v>
       </c>
       <c r="E4" t="n">
-        <v>0.417098415628316</v>
+        <v>0.596274455544577</v>
       </c>
       <c r="F4" t="n">
-        <v>41082.591</v>
+        <v>39864</v>
       </c>
       <c r="G4" t="n">
-        <v>48096.372</v>
+        <v>45519</v>
       </c>
       <c r="H4" t="n">
-        <v>54851.112</v>
+        <v>52284</v>
       </c>
       <c r="I4" t="n">
-        <v>249.191875277674</v>
+        <v>280.016773180008</v>
       </c>
       <c r="J4" t="n">
-        <v>3621.70834531902</v>
+        <v>4036.16974902457</v>
       </c>
       <c r="K4" t="n">
-        <v>606.203075849541</v>
+        <v>859.471699589223</v>
       </c>
       <c r="L4" t="n">
-        <v>4227.91142116856</v>
+        <v>4895.64144861379</v>
       </c>
       <c r="M4" t="n">
-        <v>0.151754213710275</v>
+        <v>0.153079748282477</v>
       </c>
       <c r="N4" t="n">
-        <v>0.136309731190552</v>
+        <v>0.17264550437795</v>
       </c>
       <c r="O4" t="n">
-        <v>0.149328269615015</v>
+        <v>0.156187232042559</v>
       </c>
     </row>
     <row r="5">
@@ -1105,46 +1105,46 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1500</v>
+        <v>1277</v>
       </c>
       <c r="C5" t="n">
-        <v>14.5342531613302</v>
+        <v>14.4169120855072</v>
       </c>
       <c r="D5" t="n">
-        <v>5.23161965573144</v>
+        <v>5.73010070949045</v>
       </c>
       <c r="E5" t="n">
-        <v>0.359951047890831</v>
+        <v>0.397456867011815</v>
       </c>
       <c r="F5" t="n">
-        <v>54851.112</v>
+        <v>52284</v>
       </c>
       <c r="G5" t="n">
-        <v>62816.896</v>
+        <v>59735</v>
       </c>
       <c r="H5" t="n">
-        <v>71246.112</v>
+        <v>67545</v>
       </c>
       <c r="I5" t="n">
-        <v>200.187189067182</v>
+        <v>226.737311902246</v>
       </c>
       <c r="J5" t="n">
-        <v>2909.57128555749</v>
+        <v>3268.8518921989</v>
       </c>
       <c r="K5" t="n">
-        <v>523.161965573144</v>
+        <v>573.010070949045</v>
       </c>
       <c r="L5" t="n">
-        <v>3432.73325113064</v>
+        <v>3841.86196314795</v>
       </c>
       <c r="M5" t="n">
-        <v>0.121914759714004</v>
+        <v>0.123977695673339</v>
       </c>
       <c r="N5" t="n">
-        <v>0.117637256783064</v>
+        <v>0.115102815787797</v>
       </c>
       <c r="O5" t="n">
-        <v>0.121242870386244</v>
+        <v>0.122568164399289</v>
       </c>
     </row>
     <row r="6">
@@ -1152,46 +1152,46 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>1523</v>
+        <v>1238</v>
       </c>
       <c r="C6" t="n">
-        <v>14.5372594700653</v>
+        <v>14.4115436892097</v>
       </c>
       <c r="D6" t="n">
-        <v>4.11604036177709</v>
+        <v>5.97426713563382</v>
       </c>
       <c r="E6" t="n">
-        <v>0.283137297662789</v>
+        <v>0.414547342357703</v>
       </c>
       <c r="F6" t="n">
-        <v>71246.112</v>
+        <v>67572</v>
       </c>
       <c r="G6" t="n">
-        <v>80283.036</v>
+        <v>76299</v>
       </c>
       <c r="H6" t="n">
-        <v>91182.432</v>
+        <v>86360</v>
       </c>
       <c r="I6" t="n">
-        <v>67.23531758462</v>
+        <v>136.340873307486</v>
       </c>
       <c r="J6" t="n">
-        <v>977.417257279866</v>
+        <v>1964.88245229585</v>
       </c>
       <c r="K6" t="n">
-        <v>411.604036177709</v>
+        <v>597.426713563382</v>
       </c>
       <c r="L6" t="n">
-        <v>1389.02129345758</v>
+        <v>2562.30916585923</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0409550337031057</v>
+        <v>0.0745220666882991</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0925525418189316</v>
+        <v>0.120007484064115</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0490597189836821</v>
+        <v>0.0817461777896641</v>
       </c>
     </row>
     <row r="7">
@@ -1199,46 +1199,46 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>1520</v>
+        <v>1250</v>
       </c>
       <c r="C7" t="n">
-        <v>14.5242565358897</v>
+        <v>14.4363481984637</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.643333300879124</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.044563437514453</v>
       </c>
       <c r="F7" t="n">
-        <v>91182.432</v>
+        <v>86360</v>
       </c>
       <c r="G7" t="n">
-        <v>103755.211</v>
+        <v>96780</v>
       </c>
       <c r="H7" t="n">
-        <v>117177.251</v>
+        <v>108684</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.921470541498735</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>13.3026695917027</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>64.3333300879123</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>77.635999679615</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.000504530145957053</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.0129228923147199</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.00247684639982152</v>
       </c>
     </row>
     <row r="8">
@@ -1246,10 +1246,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>1554</v>
+        <v>1287</v>
       </c>
       <c r="C8" t="n">
-        <v>14.5440209151158</v>
+        <v>14.4138303703972</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1258,13 +1258,13 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>117270.156</v>
+        <v>108856</v>
       </c>
       <c r="G8" t="n">
-        <v>133385.348</v>
+        <v>122388</v>
       </c>
       <c r="H8" t="n">
-        <v>149707.117</v>
+        <v>135688</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1293,10 +1293,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1473</v>
+        <v>1301</v>
       </c>
       <c r="C9" t="n">
-        <v>14.5319950456442</v>
+        <v>14.4284640902335</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1305,13 +1305,13 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>149714.768</v>
+        <v>135694</v>
       </c>
       <c r="G9" t="n">
-        <v>170408.537</v>
+        <v>153768</v>
       </c>
       <c r="H9" t="n">
-        <v>194759.484</v>
+        <v>179034</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1340,10 +1340,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1499</v>
+        <v>1290</v>
       </c>
       <c r="C10" t="n">
-        <v>14.5333310021416</v>
+        <v>14.42362205797</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -1352,13 +1352,13 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>194759.484</v>
+        <v>179034</v>
       </c>
       <c r="G10" t="n">
-        <v>231015.387</v>
+        <v>207072</v>
       </c>
       <c r="H10" t="n">
-        <v>286474.207</v>
+        <v>253488</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1387,10 +1387,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1533</v>
+        <v>1369</v>
       </c>
       <c r="C11" t="n">
-        <v>14.5430346394408</v>
+        <v>14.4206996786925</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -1399,13 +1399,13 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>286474.207</v>
+        <v>253488</v>
       </c>
       <c r="G11" t="n">
-        <v>438279.884</v>
+        <v>375483</v>
       </c>
       <c r="H11" t="n">
-        <v>2550288.156</v>
+        <v>4372068</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1504,49 +1504,49 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="D2" t="n">
-        <v>1.21160390870147</v>
+        <v>1.17206376329396</v>
       </c>
       <c r="E2" t="n">
-        <v>1.21160390870147</v>
+        <v>1.17206376329396</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>26.232</v>
+        <v>300</v>
       </c>
       <c r="H2" t="n">
-        <v>10964.976</v>
+        <v>11244</v>
       </c>
       <c r="I2" t="n">
-        <v>18517.606</v>
+        <v>19748</v>
       </c>
       <c r="J2" t="n">
-        <v>639.485131863176</v>
+        <v>644.621949620699</v>
       </c>
       <c r="K2" t="n">
-        <v>774.802685321901</v>
+        <v>755.538028174326</v>
       </c>
       <c r="L2" t="n">
-        <v>121.160390870147</v>
+        <v>117.206376329396</v>
       </c>
       <c r="M2" t="n">
-        <v>895.963076192049</v>
+        <v>872.744404503723</v>
       </c>
       <c r="N2" t="n">
-        <v>0.157994349106492</v>
+        <v>0.141977677132176</v>
       </c>
       <c r="O2" t="n">
-        <v>0.167402039418822</v>
+        <v>0.153760848826897</v>
       </c>
       <c r="P2" t="n">
-        <v>165.984590293497</v>
+        <v>165.962084232035</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.49445402494167</v>
+        <v>5.35883373634878</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
@@ -1560,49 +1560,49 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D3" t="n">
-        <v>1.23897781400707</v>
+        <v>1.16793389840701</v>
       </c>
       <c r="E3" t="n">
-        <v>1.23897781400707</v>
+        <v>1.16793389840701</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>18808.344</v>
+        <v>19872</v>
       </c>
       <c r="H3" t="n">
-        <v>23124.601</v>
+        <v>24880</v>
       </c>
       <c r="I3" t="n">
-        <v>28710.924</v>
+        <v>28600</v>
       </c>
       <c r="J3" t="n">
-        <v>846.206308143556</v>
+        <v>861.32456872776</v>
       </c>
       <c r="K3" t="n">
-        <v>1048.43084186269</v>
+        <v>1005.97016134795</v>
       </c>
       <c r="L3" t="n">
-        <v>123.897781400707</v>
+        <v>116.793389840701</v>
       </c>
       <c r="M3" t="n">
-        <v>1172.3286232634</v>
+        <v>1122.76355118865</v>
       </c>
       <c r="N3" t="n">
-        <v>0.213791396934109</v>
+        <v>0.189037879559263</v>
       </c>
       <c r="O3" t="n">
-        <v>0.171184172789393</v>
+        <v>0.153219059591153</v>
       </c>
       <c r="P3" t="n">
-        <v>128.263155586076</v>
+        <v>124.683089264767</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.37150518243355</v>
+        <v>3.22360684853305</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
@@ -1616,49 +1616,49 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="D4" t="n">
-        <v>1.22701921292254</v>
+        <v>1.17630008382046</v>
       </c>
       <c r="E4" t="n">
-        <v>1.22701921292254</v>
+        <v>1.17630008382046</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>28828.968</v>
+        <v>28752</v>
       </c>
       <c r="H4" t="n">
-        <v>33904.86</v>
+        <v>32376</v>
       </c>
       <c r="I4" t="n">
-        <v>38364.3</v>
+        <v>37737</v>
       </c>
       <c r="J4" t="n">
-        <v>882.273781106785</v>
+        <v>908.004856848582</v>
       </c>
       <c r="K4" t="n">
-        <v>1082.56688047584</v>
+        <v>1068.08618922037</v>
       </c>
       <c r="L4" t="n">
-        <v>122.701921292254</v>
+        <v>117.630008382046</v>
       </c>
       <c r="M4" t="n">
-        <v>1205.2688017681</v>
+        <v>1185.71619760242</v>
       </c>
       <c r="N4" t="n">
-        <v>0.220752267493712</v>
+        <v>0.200710474479885</v>
       </c>
       <c r="O4" t="n">
-        <v>0.169531904918872</v>
+        <v>0.154316603778511</v>
       </c>
       <c r="P4" t="n">
-        <v>94.8207726180492</v>
+        <v>101.991145419457</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.11053114982056</v>
+        <v>3.02840768382573</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
@@ -1672,49 +1672,49 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D5" t="n">
-        <v>1.23111539109937</v>
+        <v>1.18222504641062</v>
       </c>
       <c r="E5" t="n">
-        <v>1.23111539109937</v>
+        <v>1.18222504641062</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>38602.574</v>
+        <v>37739</v>
       </c>
       <c r="H5" t="n">
-        <v>42692.58</v>
+        <v>41073</v>
       </c>
       <c r="I5" t="n">
-        <v>46037.16</v>
+        <v>44085</v>
       </c>
       <c r="J5" t="n">
-        <v>797.123131909767</v>
+        <v>877.047561782743</v>
       </c>
       <c r="K5" t="n">
-        <v>981.350556295445</v>
+        <v>1036.86759443293</v>
       </c>
       <c r="L5" t="n">
-        <v>123.111539109937</v>
+        <v>118.222504641062</v>
       </c>
       <c r="M5" t="n">
-        <v>1104.46209540538</v>
+        <v>1155.09009907399</v>
       </c>
       <c r="N5" t="n">
-        <v>0.200112680717899</v>
+        <v>0.194844001309815</v>
       </c>
       <c r="O5" t="n">
-        <v>0.170097856031854</v>
+        <v>0.155093888518183</v>
       </c>
       <c r="P5" t="n">
-        <v>67.5596189058994</v>
+        <v>75.6635259393802</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.46705241981072</v>
+        <v>3.21778482450129</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
@@ -1728,49 +1728,49 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="D6" t="n">
-        <v>1.18001422125303</v>
+        <v>1.1442902418653</v>
       </c>
       <c r="E6" t="n">
-        <v>1.18001422125303</v>
+        <v>1.1442902418653</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>46151.925</v>
+        <v>44184</v>
       </c>
       <c r="H6" t="n">
-        <v>50839.802</v>
+        <v>48000</v>
       </c>
       <c r="I6" t="n">
-        <v>54929.808</v>
+        <v>51257</v>
       </c>
       <c r="J6" t="n">
-        <v>602.694731190546</v>
+        <v>728.187678937758</v>
       </c>
       <c r="K6" t="n">
-        <v>711.188353879117</v>
+        <v>833.258055255015</v>
       </c>
       <c r="L6" t="n">
-        <v>118.001422125303</v>
+        <v>114.42902418653</v>
       </c>
       <c r="M6" t="n">
-        <v>829.18977600442</v>
+        <v>947.687079441545</v>
       </c>
       <c r="N6" t="n">
-        <v>0.145022394981202</v>
+        <v>0.156582513024063</v>
       </c>
       <c r="O6" t="n">
-        <v>0.163037429775775</v>
+        <v>0.150117292594272</v>
       </c>
       <c r="P6" t="n">
-        <v>42.2854099792372</v>
+        <v>54.6940628902259</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.65163472428207</v>
+        <v>3.80906669434067</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
@@ -1784,49 +1784,49 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="D7" t="n">
-        <v>1.27877796566927</v>
+        <v>1.21234569742025</v>
       </c>
       <c r="E7" t="n">
-        <v>1.14895850830196</v>
+        <v>1.21234569742025</v>
       </c>
       <c r="F7" t="n">
-        <v>0.898481627888106</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>55060.968</v>
+        <v>51397</v>
       </c>
       <c r="H7" t="n">
-        <v>59778.356</v>
+        <v>56350</v>
       </c>
       <c r="I7" t="n">
-        <v>65580</v>
+        <v>61138</v>
       </c>
       <c r="J7" t="n">
-        <v>239.017676531937</v>
+        <v>457.044376384633</v>
       </c>
       <c r="K7" t="n">
-        <v>305.650538154505</v>
+        <v>554.095783240031</v>
       </c>
       <c r="L7" t="n">
-        <v>114.895850830196</v>
+        <v>121.234569742025</v>
       </c>
       <c r="M7" t="n">
-        <v>420.546388984701</v>
+        <v>675.330352982056</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0623269107665869</v>
+        <v>0.104123458091512</v>
       </c>
       <c r="O7" t="n">
-        <v>0.158746597065284</v>
+        <v>0.159045360282349</v>
       </c>
       <c r="P7" t="n">
-        <v>14.5563409421775</v>
+        <v>29.4168842471715</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.492216889978</v>
+        <v>6.03266776224253</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
@@ -1840,43 +1840,43 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="D8" t="n">
-        <v>1.22912405460904</v>
+        <v>1.17380458668203</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.567482352231819</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.483455558676857</v>
       </c>
       <c r="G8" t="n">
-        <v>65684.928</v>
+        <v>61224</v>
       </c>
       <c r="H8" t="n">
-        <v>70313.783</v>
+        <v>66490</v>
       </c>
       <c r="I8" t="n">
-        <v>78515.655</v>
+        <v>74853</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>57.6851461599572</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>67.7110891459812</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>56.7482352231819</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>124.459324369163</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.0127239964032862</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.0744469464086352</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1892,10 +1892,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>1.22364555151963</v>
+        <v>1.17586037997763</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>78696</v>
+        <v>75042</v>
       </c>
       <c r="H9" t="n">
-        <v>86919.732</v>
+        <v>81684</v>
       </c>
       <c r="I9" t="n">
-        <v>103904.952</v>
+        <v>94627</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1944,10 +1944,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="D10" t="n">
-        <v>1.23325170163468</v>
+        <v>1.150339396187</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>104062.344</v>
+        <v>94669</v>
       </c>
       <c r="H10" t="n">
-        <v>115971.672</v>
+        <v>106673</v>
       </c>
       <c r="I10" t="n">
-        <v>140946.722</v>
+        <v>123564</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1996,10 +1996,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="D11" t="n">
-        <v>1.22876427107846</v>
+        <v>1.20395356838908</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>141390.48</v>
+        <v>123795</v>
       </c>
       <c r="H11" t="n">
-        <v>202655.316</v>
+        <v>169596</v>
       </c>
       <c r="I11" t="n">
-        <v>1410940.584</v>
+        <v>1087452</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -2048,49 +2048,49 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>776</v>
+        <v>702</v>
       </c>
       <c r="D12" t="n">
-        <v>7.094094652971</v>
+        <v>7.08972444230963</v>
       </c>
       <c r="E12" t="n">
-        <v>7.094094652971</v>
+        <v>7.08972444230963</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>-141188.275</v>
+        <v>-49518</v>
       </c>
       <c r="H12" t="n">
-        <v>41866.272</v>
+        <v>39404</v>
       </c>
       <c r="I12" t="n">
-        <v>56989.02</v>
+        <v>55875</v>
       </c>
       <c r="J12" t="n">
-        <v>745.658178018356</v>
+        <v>734.805023768163</v>
       </c>
       <c r="K12" t="n">
-        <v>5289.76969362412</v>
+        <v>5209.56513734106</v>
       </c>
       <c r="L12" t="n">
-        <v>709.4094652971</v>
+        <v>708.972444230963</v>
       </c>
       <c r="M12" t="n">
-        <v>5999.17915892122</v>
+        <v>5918.53758157202</v>
       </c>
       <c r="N12" t="n">
-        <v>0.637035867065899</v>
+        <v>0.562867492057047</v>
       </c>
       <c r="O12" t="n">
-        <v>0.487284516477901</v>
+        <v>0.419438871128915</v>
       </c>
       <c r="P12" t="n">
-        <v>102.592235840468</v>
+        <v>110.536950845726</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.32820498414718</v>
+        <v>2.29589598821062</v>
       </c>
       <c r="R12" t="b">
         <v>1</v>
@@ -2104,49 +2104,49 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>839</v>
+        <v>652</v>
       </c>
       <c r="D13" t="n">
-        <v>7.09208927230334</v>
+        <v>7.09348220104188</v>
       </c>
       <c r="E13" t="n">
-        <v>7.09208927230334</v>
+        <v>7.09348220104188</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>57015.252</v>
+        <v>56031</v>
       </c>
       <c r="H13" t="n">
-        <v>71724.846</v>
+        <v>69216</v>
       </c>
       <c r="I13" t="n">
-        <v>84716.244</v>
+        <v>79561</v>
       </c>
       <c r="J13" t="n">
-        <v>424.181890552559</v>
+        <v>519.603443600065</v>
       </c>
       <c r="K13" t="n">
-        <v>3008.33583549315</v>
+        <v>3685.79777877713</v>
       </c>
       <c r="L13" t="n">
-        <v>709.208927230334</v>
+        <v>709.348220104188</v>
       </c>
       <c r="M13" t="n">
-        <v>3717.54476272349</v>
+        <v>4395.14599888132</v>
       </c>
       <c r="N13" t="n">
-        <v>0.362287573634576</v>
+        <v>0.398232039964202</v>
       </c>
       <c r="O13" t="n">
-        <v>0.487146769380238</v>
+        <v>0.41966118584558</v>
       </c>
       <c r="P13" t="n">
-        <v>33.1220681997491</v>
+        <v>42.8516290157793</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.2093295531895</v>
+        <v>3.3715233038466</v>
       </c>
       <c r="R13" t="b">
         <v>0</v>
@@ -2160,43 +2160,43 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>769</v>
+        <v>619</v>
       </c>
       <c r="D14" t="n">
-        <v>7.09595053984403</v>
+        <v>7.09366981634319</v>
       </c>
       <c r="E14" t="n">
-        <v>0.372240184416668</v>
+        <v>2.71967225108125</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0524581142901892</v>
+        <v>0.383394254524698</v>
       </c>
       <c r="G14" t="n">
-        <v>84720.616</v>
+        <v>79561</v>
       </c>
       <c r="H14" t="n">
-        <v>95576.292</v>
+        <v>90265</v>
       </c>
       <c r="I14" t="n">
-        <v>107827.729</v>
+        <v>100236</v>
       </c>
       <c r="J14" t="n">
-        <v>0.79171371285735</v>
+        <v>50.7550385126371</v>
       </c>
       <c r="K14" t="n">
-        <v>5.61796134815203</v>
+        <v>360.03948472443</v>
       </c>
       <c r="L14" t="n">
-        <v>37.2240184416668</v>
+        <v>271.967225108125</v>
       </c>
       <c r="M14" t="n">
-        <v>42.8419797898188</v>
+        <v>632.006709832554</v>
       </c>
       <c r="N14" t="n">
-        <v>0.000676559299524212</v>
+        <v>0.0389004679787506</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0255687141418611</v>
+        <v>0.160899943025505</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -2212,10 +2212,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>822</v>
+        <v>672</v>
       </c>
       <c r="D15" t="n">
-        <v>7.0860420659288</v>
+        <v>7.0898048931916</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -2224,13 +2224,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>107827.729</v>
+        <v>100240</v>
       </c>
       <c r="H15" t="n">
-        <v>120264.976</v>
+        <v>110146</v>
       </c>
       <c r="I15" t="n">
-        <v>131737.104</v>
+        <v>120661</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2264,10 +2264,10 @@
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>741</v>
+        <v>623</v>
       </c>
       <c r="D16" t="n">
-        <v>7.10629294479592</v>
+        <v>7.09386021837777</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -2276,13 +2276,13 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>131750.22</v>
+        <v>120661</v>
       </c>
       <c r="H16" t="n">
-        <v>142417.9</v>
+        <v>128972</v>
       </c>
       <c r="I16" t="n">
-        <v>154780.823</v>
+        <v>139652</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2316,10 +2316,10 @@
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>703</v>
+        <v>641</v>
       </c>
       <c r="D17" t="n">
-        <v>7.09211684523508</v>
+        <v>7.09016305270614</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -2328,13 +2328,13 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>154780.823</v>
+        <v>139652</v>
       </c>
       <c r="H17" t="n">
-        <v>168234.56</v>
+        <v>151743</v>
       </c>
       <c r="I17" t="n">
-        <v>181274.05</v>
+        <v>166140</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2368,10 +2368,10 @@
         <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>728</v>
+        <v>641</v>
       </c>
       <c r="D18" t="n">
-        <v>7.09558636846366</v>
+        <v>7.09609430059273</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -2380,13 +2380,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>181274.05</v>
+        <v>166200</v>
       </c>
       <c r="H18" t="n">
-        <v>198228.666</v>
+        <v>181032</v>
       </c>
       <c r="I18" t="n">
-        <v>218698.37</v>
+        <v>197388</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2420,10 +2420,10 @@
         <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>714</v>
+        <v>636</v>
       </c>
       <c r="D19" t="n">
-        <v>7.09701955454404</v>
+        <v>7.08752479675841</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2432,13 +2432,13 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>218761.764</v>
+        <v>197400</v>
       </c>
       <c r="H19" t="n">
-        <v>241966.154</v>
+        <v>216792</v>
       </c>
       <c r="I19" t="n">
-        <v>273817.267</v>
+        <v>242567</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2472,10 +2472,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>731</v>
+        <v>666</v>
       </c>
       <c r="D20" t="n">
-        <v>7.09365689249796</v>
+        <v>7.08503917291069</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>273835.848</v>
+        <v>242567</v>
       </c>
       <c r="H20" t="n">
-        <v>324321.518</v>
+        <v>284350</v>
       </c>
       <c r="I20" t="n">
-        <v>414943.241</v>
+        <v>354924</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2524,10 +2524,10 @@
         <v>10</v>
       </c>
       <c r="C21" t="n">
-        <v>771</v>
+        <v>679</v>
       </c>
       <c r="D21" t="n">
-        <v>7.09791593959024</v>
+        <v>7.1112860579813</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -2536,13 +2536,13 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>414943.241</v>
+        <v>356001</v>
       </c>
       <c r="H21" t="n">
-        <v>575185.785</v>
+        <v>529334</v>
       </c>
       <c r="I21" t="n">
-        <v>2550288.156</v>
+        <v>4372068</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2576,49 +2576,49 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>612</v>
+        <v>479</v>
       </c>
       <c r="D22" t="n">
-        <v>6.20005808201142</v>
+        <v>6.14866406138384</v>
       </c>
       <c r="E22" t="n">
-        <v>6.20005808201142</v>
+        <v>6.14866406138384</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>21.86</v>
+        <v>-132</v>
       </c>
       <c r="H22" t="n">
-        <v>12197.88</v>
+        <v>11877</v>
       </c>
       <c r="I22" t="n">
-        <v>19282.706</v>
+        <v>18312</v>
       </c>
       <c r="J22" t="n">
-        <v>574.75040123231</v>
+        <v>570.165202694506</v>
       </c>
       <c r="K22" t="n">
-        <v>3563.48587029969</v>
+        <v>3505.75429085934</v>
       </c>
       <c r="L22" t="n">
-        <v>620.005808201143</v>
+        <v>614.866406138384</v>
       </c>
       <c r="M22" t="n">
-        <v>4183.49167850084</v>
+        <v>4120.62069699772</v>
       </c>
       <c r="N22" t="n">
-        <v>0.334351397679096</v>
+        <v>0.29736186511363</v>
       </c>
       <c r="O22" t="n">
-        <v>0.273415058276327</v>
+        <v>0.243444588032127</v>
       </c>
       <c r="P22" t="n">
-        <v>143.239836673957</v>
+        <v>146.0687932796</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.7233700468273</v>
+        <v>5.76415701041788</v>
       </c>
       <c r="R22" t="b">
         <v>0</v>
@@ -2632,49 +2632,49 @@
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>610</v>
+        <v>505</v>
       </c>
       <c r="D23" t="n">
-        <v>6.20930595163854</v>
+        <v>6.15162036075793</v>
       </c>
       <c r="E23" t="n">
-        <v>6.20930595163854</v>
+        <v>6.15162036075793</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>19290.357</v>
+        <v>18322</v>
       </c>
       <c r="H23" t="n">
-        <v>24618.732</v>
+        <v>23522</v>
       </c>
       <c r="I23" t="n">
-        <v>29524.116</v>
+        <v>28172</v>
       </c>
       <c r="J23" t="n">
-        <v>623.223526179425</v>
+        <v>644.721077920743</v>
       </c>
       <c r="K23" t="n">
-        <v>3869.78555030706</v>
+        <v>3966.07930994704</v>
       </c>
       <c r="L23" t="n">
-        <v>620.930595163854</v>
+        <v>615.162036075793</v>
       </c>
       <c r="M23" t="n">
-        <v>4490.71614547091</v>
+        <v>4581.24134602283</v>
       </c>
       <c r="N23" t="n">
-        <v>0.363090595713438</v>
+        <v>0.336407130376881</v>
       </c>
       <c r="O23" t="n">
-        <v>0.273822878135364</v>
+        <v>0.24356163704896</v>
       </c>
       <c r="P23" t="n">
-        <v>85.4421219752872</v>
+        <v>93.1910546032467</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.75403411337569</v>
+        <v>4.56196057651548</v>
       </c>
       <c r="R23" t="b">
         <v>0</v>
@@ -2688,49 +2688,49 @@
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>584</v>
+        <v>523</v>
       </c>
       <c r="D24" t="n">
-        <v>6.22055767182167</v>
+        <v>6.13786716521722</v>
       </c>
       <c r="E24" t="n">
-        <v>6.22055767182167</v>
+        <v>6.13786716521722</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>29589.696</v>
+        <v>28175</v>
       </c>
       <c r="H24" t="n">
-        <v>34101.6</v>
+        <v>32306</v>
       </c>
       <c r="I24" t="n">
-        <v>37747.848</v>
+        <v>36121</v>
       </c>
       <c r="J24" t="n">
-        <v>420.772466959569</v>
+        <v>488.000858556684</v>
       </c>
       <c r="K24" t="n">
-        <v>2617.43939743668</v>
+        <v>2995.28444633289</v>
       </c>
       <c r="L24" t="n">
-        <v>622.055767182167</v>
+        <v>613.786716521722</v>
       </c>
       <c r="M24" t="n">
-        <v>3239.49516461884</v>
+        <v>3609.07116285461</v>
       </c>
       <c r="N24" t="n">
-        <v>0.245586639803256</v>
+        <v>0.254063261600991</v>
       </c>
       <c r="O24" t="n">
-        <v>0.274319065378917</v>
+        <v>0.243017105588287</v>
       </c>
       <c r="P24" t="n">
-        <v>41.315672421815</v>
+        <v>53.3045748666137</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.09758199854391</v>
+        <v>5.80700670251319</v>
       </c>
       <c r="R24" t="b">
         <v>0</v>
@@ -2744,49 +2744,49 @@
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>617</v>
+        <v>502</v>
       </c>
       <c r="D25" t="n">
-        <v>6.20768140841987</v>
+        <v>6.10485270795255</v>
       </c>
       <c r="E25" t="n">
-        <v>4.04643753054872</v>
+        <v>6.10485270795255</v>
       </c>
       <c r="F25" t="n">
-        <v>0.651843621526756</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>37760.964</v>
+        <v>36121</v>
       </c>
       <c r="H25" t="n">
-        <v>41339.446</v>
+        <v>40118</v>
       </c>
       <c r="I25" t="n">
-        <v>45840.42</v>
+        <v>43344</v>
       </c>
       <c r="J25" t="n">
-        <v>97.8135715526791</v>
+        <v>214.292959941081</v>
       </c>
       <c r="K25" t="n">
-        <v>607.195489618713</v>
+        <v>1308.22695679147</v>
       </c>
       <c r="L25" t="n">
-        <v>404.643753054872</v>
+        <v>610.485270795255</v>
       </c>
       <c r="M25" t="n">
-        <v>1011.83924267358</v>
+        <v>1918.71222758673</v>
       </c>
       <c r="N25" t="n">
-        <v>0.056971366804209</v>
+        <v>0.110965223340876</v>
       </c>
       <c r="O25" t="n">
-        <v>0.178442998209392</v>
+        <v>0.241709961326109</v>
       </c>
       <c r="P25" t="n">
-        <v>7.63594110057332</v>
+        <v>17.8317629696901</v>
       </c>
       <c r="Q25" t="n">
-        <v>31.6790958493616</v>
+        <v>13.9786890196711</v>
       </c>
       <c r="R25" t="b">
         <v>0</v>
@@ -2800,43 +2800,43 @@
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>617</v>
+        <v>539</v>
       </c>
       <c r="D26" t="n">
-        <v>6.20384585417633</v>
+        <v>6.211138008334</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.713930398066857</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.114943573481851</v>
       </c>
       <c r="G26" t="n">
-        <v>45866.652</v>
+        <v>43348</v>
       </c>
       <c r="H26" t="n">
-        <v>50155.584</v>
+        <v>47404</v>
       </c>
       <c r="I26" t="n">
-        <v>54798.648</v>
+        <v>51864</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2.28253357777812</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>14.1771310602363</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>71.3930398066857</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>85.570170866922</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>0.00120251956762174</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>0.028266708004516</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>621</v>
+        <v>508</v>
       </c>
       <c r="D27" t="n">
-        <v>6.22270586367064</v>
+        <v>6.11791375883276</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -2864,13 +2864,13 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>54798.648</v>
+        <v>51900</v>
       </c>
       <c r="H27" t="n">
-        <v>60281.136</v>
+        <v>55824</v>
       </c>
       <c r="I27" t="n">
-        <v>66183.336</v>
+        <v>61927</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2904,10 +2904,10 @@
         <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>597</v>
+        <v>527</v>
       </c>
       <c r="D28" t="n">
-        <v>6.20677918418525</v>
+        <v>6.16798203650481</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -2916,13 +2916,13 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>66183.336</v>
+        <v>61929</v>
       </c>
       <c r="H28" t="n">
-        <v>72357.693</v>
+        <v>68083</v>
       </c>
       <c r="I28" t="n">
-        <v>79958.415</v>
+        <v>75036</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>8</v>
       </c>
       <c r="C29" t="n">
-        <v>618</v>
+        <v>520</v>
       </c>
       <c r="D29" t="n">
-        <v>6.21502896765521</v>
+        <v>6.17175702689714</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2968,13 +2968,13 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>79959.508</v>
+        <v>75096</v>
       </c>
       <c r="H29" t="n">
-        <v>89337.448</v>
+        <v>84120</v>
       </c>
       <c r="I29" t="n">
-        <v>101163.708</v>
+        <v>95116</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3008,10 +3008,10 @@
         <v>9</v>
       </c>
       <c r="C30" t="n">
-        <v>608</v>
+        <v>519</v>
       </c>
       <c r="D30" t="n">
-        <v>6.21038298532052</v>
+        <v>6.14563031740919</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -3020,13 +3020,13 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>101399.796</v>
+        <v>95268</v>
       </c>
       <c r="H30" t="n">
-        <v>117429.734</v>
+        <v>110155</v>
       </c>
       <c r="I30" t="n">
-        <v>142479.108</v>
+        <v>132122</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3060,10 +3060,10 @@
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>658</v>
+        <v>546</v>
       </c>
       <c r="D31" t="n">
-        <v>6.21534117667787</v>
+        <v>6.15829414163229</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -3072,13 +3072,13 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>142479.108</v>
+        <v>132480</v>
       </c>
       <c r="H31" t="n">
-        <v>190485.854</v>
+        <v>170952</v>
       </c>
       <c r="I31" t="n">
-        <v>1732558.02</v>
+        <v>1554636</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
